--- a/bench/data/files/synthetic1_A.xlsx
+++ b/bench/data/files/synthetic1_A.xlsx
@@ -549,17 +549,17 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Wavelength SA</t>
+          <t>Atlas Corp</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -569,35 +569,35 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2010-04-12</t>
+          <t>2013-05-21</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2014-06-04</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>698.1</v>
+        <v>1121.8</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1495.9</v>
+        <v>1617.5</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>176.3</v>
+        <v>206.3</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>230.2</v>
+        <v>482.7</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>146.9</v>
+        <v>134.5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.299</v>
+        <v>0.783</v>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Hannah Nakamura; Rachel Johnson; Priya Ueno; Emma Rossi; Laura Patel</t>
+          <t>Christopher Mueller; Emma Nakamura; Hannah O'Brien; James Anderson</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -609,12 +609,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Vertex Group</t>
+          <t>Delta Labs</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -629,35 +629,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2013-10-11</t>
+          <t>2010-11-04</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
+          <t>2017-11-11</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1217</v>
+        <v>1279.9</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2200.1</v>
+        <v>2826.6</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>194</v>
+        <v>218.2</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>320.1</v>
+        <v>294.1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>830.9</v>
+        <v>914.6</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.409</v>
+        <v>0.875</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>David Anderson; Matthew Ivanov; Mark Yamamoto; Laura Nakamura</t>
+          <t>Sarah Nakamura; Sophie Anderson; Yuki Xu; Sarah Nakamura</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -669,17 +669,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Orion Systems</t>
+          <t>Umbra Foods</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -689,35 +689,35 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2010-09-28</t>
+          <t>2010-10-06</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
+          <t>2013-10-20</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>277.9</v>
+        <v>829.7</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>291.5</v>
+        <v>2228</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>25.7</v>
+        <v>229.8</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>23.4</v>
+        <v>424.4</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>97.8</v>
+        <v>526.3</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.283</v>
+        <v>0.63</v>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Robert Anderson; Hannah Williams; Matthew Qureshi; Hannah Hassan</t>
+          <t>David Gupta; Sophie Chen; Jennifer Evans</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -729,17 +729,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Beacon GmbH</t>
+          <t>Zenith Capital</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -749,35 +749,35 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2012-09-21</t>
+          <t>2011-12-24</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>2018-09-28</t>
+          <t>2019-12-24</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>471.5</v>
+        <v>451.7</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>382.9</v>
+        <v>714.4</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>100.5</v>
+        <v>85.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>122.3</v>
+        <v>141.1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>301.9</v>
+        <v>336.4</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.758</v>
+        <v>0.432</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Michael Brown; Rachel Evans</t>
+          <t>Jennifer Patel; Ravi Mueller</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -789,17 +789,17 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Glacier Bio</t>
+          <t>Atlas Health</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -809,35 +809,35 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2013-12-26</t>
+          <t>2011-03-22</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2017-02-26</t>
+          <t>2019-04-17</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>246.7</v>
+        <v>789.1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>659.9</v>
+        <v>1130.8</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>112.7</v>
+        <v>171.2</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>193.2</v>
+        <v>118</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.526</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Mark Ivanov; Yuki Yamamoto; Michael Nakamura</t>
+          <t>Ahmed Chen; Priya Johnson; James Evans; Olivia O'Brien</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -849,17 +849,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Yields Logistics</t>
+          <t>Stratus Networks</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -869,35 +869,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2013-01-03</t>
+          <t>2012-07-01</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>2019-12-06</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1366.8</v>
+        <v>1357.1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1818.1</v>
+        <v>1163.2</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>192.2</v>
+        <v>325.1</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>162.2</v>
+        <v>353</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>338</v>
+        <v>933.5</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.535</v>
+        <v>0.797</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Daniel Williams; Sarah Kim; Jennifer Nakamura</t>
+          <t>Wei Evans; Sophie Johnson; Rachel Patel</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -909,55 +909,51 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Lattice Solutions</t>
+          <t>Xenith SA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2012-06-15</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>2017-05-26</t>
-        </is>
-      </c>
+          <t>2011-08-22</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
-        <v>1724.8</v>
+        <v>711.6</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4557.5</v>
+        <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>277.9</v>
+        <v>92</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>600.1</v>
+        <v/>
       </c>
       <c r="K11" s="4" t="n">
-        <v>770.2</v>
+        <v>229.9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.495</v>
+        <v>0.175</v>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Elena Qureshi; Olivia Fischer; Olivia O'Brien; Ahmed Gupta</t>
+          <t>Rachel Xu; Jessica Gupta; Olivia Chen; Olivia Johnson; Amanda Johnson</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -969,17 +965,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Drift Foods</t>
+          <t>Radial Logic</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -989,35 +985,35 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2012-10-08</t>
+          <t>2012-12-09</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>2016-11-27</t>
+          <t>2016-11-24</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>388</v>
+        <v>1957.9</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>601.2</v>
+        <v>4213.6</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>61.4</v>
+        <v>478.1</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>67.8</v>
+        <v>470.3</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>250.7</v>
+        <v>2048.5</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.358</v>
+        <v>0.191</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Laura Davis; Olivia Zhang; Mark Kim</t>
+          <t>Matthew Zhang; Sarah Yamamoto</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1029,17 +1025,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Delta Logic</t>
+          <t>Mosaic Tech</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1049,57 +1045,57 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2013-11-25</t>
+          <t>2013-04-28</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>515</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>934.4</v>
+        <v>196.4</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>101.4</v>
+        <v>14.5</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>183.2</v>
+        <v>14.2</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>415.1</v>
+        <v>14.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.903</v>
+        <v>0.97</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>David Vega; Emma Ueno; James Zhang; Wei Schmidt</t>
+          <t>Yuki Chen; Ravi Gupta; James Ivanov; Ahmed Nakamura; Michael Ivanov</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Fund I</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Junction Foods</t>
+          <t>Zenith Labs</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1109,113 +1105,117 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2013-02-10</t>
+          <t>2014-04-10</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2018-03-03</t>
+          <t>2019-03-11</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1109.2</v>
+        <v>895.9</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1433.9</v>
+        <v>2321.5</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>173.9</v>
+        <v>104</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>342</v>
+        <v>218.3</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>755.1</v>
+        <v>75</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.883</v>
+        <v>0.721</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Amanda Ueno; Ravi Brown; Daniel Brown; Jennifer Kim</t>
+          <t>Jennifer Rossi; Thomas Vega; Matthew Xu; Robert Tanaka</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Fund I</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Lumen Ltd</t>
+          <t>Helix Holdings</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2013-03-18</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
+          <t>2014-06-22</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>2021-07-14</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="n">
-        <v>153.2</v>
+        <v>1118.1</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v/>
+        <v>3135.5</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>22.8</v>
+        <v>169</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v/>
+        <v>327.1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>75</v>
+        <v>309.4</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.709</v>
+        <v>0.751</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Sarah Qureshi; Hannah Yamamoto; Jennifer Vega; Ravi Yamamoto</t>
+          <t>Christopher Evans; Andrew Johnson; Rachel Johnson</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Fund I</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Bloom Industries</t>
+          <t>Cipher Logic</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1225,57 +1225,57 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2012-10-16</t>
+          <t>2014-12-05</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
+          <t>2021-11-24</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>518.1</v>
+        <v>1381.4</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>870.9</v>
+        <v>4559.2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>118.3</v>
+        <v>341.4</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>157</v>
+        <v>513.1</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>252.3</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.902</v>
+        <v>0.321</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Amanda Vega; Rachel Qureshi</t>
+          <t>Ahmed Qureshi; Robert Vega</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Fund I</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Drift Ltd</t>
+          <t>Tessera Materials</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2011-05-15</t>
+          <t>2012-09-17</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>2016-08-06</t>
+          <t>2020-11-18</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1593.2</v>
+        <v>1709.5</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4062.8</v>
+        <v>4877.3</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>213.4</v>
+        <v>285.2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>241.1</v>
+        <v>331.3</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>756.1</v>
+        <v>1053.6</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.733</v>
+        <v>0.714</v>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Wei Lopez; Yuki Vega</t>
+          <t>Jennifer Nakamura; Hannah Hassan; Jennifer Hassan</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>Fund I</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Forge SA</t>
+          <t>Forge Holdings</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1345,57 +1345,57 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2010-01-05</t>
+          <t>2013-08-17</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>2014-10-22</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1781.9</v>
+        <v>1067.5</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5788.5</v>
+        <v>2514.3</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>222.6</v>
+        <v>296.2</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>399.3</v>
+        <v>505.4</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>382.8</v>
+        <v>363.7</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.974</v>
+        <v>0.663</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Hannah Mueller; Sophie Hassan</t>
+          <t>Thomas Kim; Ravi Vega; Daniel Hassan; Jennifer Mueller; Christopher Davis</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Fund I</t>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Junction Capital</t>
+          <t>Kepler Holdings</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1405,35 +1405,35 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2012-04-24</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1293.6</v>
+        <v>881.6</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2516.3</v>
+        <v>1733</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>117.5</v>
+        <v>96.8</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>187.8</v>
+        <v>168.6</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>378.6</v>
+        <v>180.8</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.393</v>
+        <v>0.726</v>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Sarah Fischer; Elena Tanaka; Andrew Yamamoto; Hannah Gupta</t>
+          <t>Matthew Ivanov; Jessica Yamamoto; Thomas Lopez; Sophie Zhang</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1445,17 +1445,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Wavelength Inc</t>
+          <t>Apex Health</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2012-06-18</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2018-09-12</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>628</v>
+        <v>1364</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1377.4</v>
+        <v>3739.4</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>133.2</v>
+        <v>164.3</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>289.3</v>
+        <v>371.4</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>491.3</v>
+        <v>395.4</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.212</v>
+        <v>0.958</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Wei Patel; Andrew Nakamura; Michael Xu; Jennifer Schmidt</t>
+          <t>Priya Mueller; Ahmed Davis; Ravi Qureshi; Michael Ueno</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1505,17 +1505,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Polaris Group</t>
+          <t>Cipher Media</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1525,35 +1525,35 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2014-05-03</t>
+          <t>2015-09-20</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2017-06-08</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1883</v>
+        <v>211.2</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6264</v>
+        <v>432.6</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>451.5</v>
+        <v>56</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>693.8</v>
+        <v>102.4</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1257.1</v>
+        <v>225.7</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.758</v>
+        <v>0.894</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Thomas Gupta; Mark Johnson; Hannah Johnson</t>
+          <t>Emma Yamamoto; Priya Ueno</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1565,17 +1565,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Stratus Networks</t>
+          <t>Fathom Media</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1585,35 +1585,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2013-02-10</t>
+          <t>2013-11-12</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2015-12-03</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>986.2</v>
+        <v>1107.5</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1444</v>
+        <v>1978.7</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>190.7</v>
+        <v>243.2</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>458.5</v>
+        <v>313</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>447.8</v>
+        <v>954.9</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.235</v>
+        <v>0.651</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Olivia Hassan; Ravi Kim; Olivia Qureshi; Rachel Brown; Jennifer Rossi</t>
+          <t>Michael Davis; Thomas Rossi; Elena Johnson; David Chen</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -1625,17 +1625,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Lattice Networks</t>
+          <t>Glacier Dynamics</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1645,35 +1645,35 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2013-07-25</t>
+          <t>2015-11-11</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2017-06-07</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1557.7</v>
+        <v>327.4</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3844.1</v>
+        <v>247.4</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>294.6</v>
+        <v>87</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>282.9</v>
+        <v>179.1</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>887</v>
+        <v>295.2</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.529</v>
+        <v>0.268</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Hannah Nakamura; Sarah Chen; Sarah Xu</t>
+          <t>Jennifer Ivanov; Jessica Evans; Amanda Patel; Olivia Xu</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -1685,17 +1685,17 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Meridian Corp</t>
+          <t>Zenith Materials</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1705,113 +1705,117 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2015-09-19</t>
+          <t>2017-08-10</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>2019-10-19</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>627.3</v>
+        <v>663.5</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1715.5</v>
+        <v>1028.9</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>88.5</v>
+        <v>163.1</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>77.90000000000001</v>
+        <v>157.7</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>357.4</v>
+        <v>702</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.392</v>
+        <v>0.791</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Jessica Lopez; Rachel Qureshi; Jessica Vega</t>
+          <t>Yuki O'Brien; James Ivanov; Elena Patel</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Lattice Holdings</t>
+          <t>Bloom SA</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2015-08-26</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
+          <t>2014-11-15</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="n">
-        <v>1788.6</v>
+        <v>1993.8</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v/>
+        <v>4573.7</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>264.1</v>
+        <v>521.9</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v/>
+        <v>513.1</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>549.3</v>
+        <v>671.8</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.306</v>
+        <v>0.372</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Michael Xu; Thomas Lopez; Olivia Ivanov; Matthew Fischer</t>
+          <t>Sophie Tanaka; Michael Johnson; Ahmed Williams; Emma Davis</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Gravity Logic</t>
+          <t>Quanta AG</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1821,57 +1825,57 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2015-02-02</t>
+          <t>2015-08-26</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>2019-03-31</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1606.8</v>
+        <v>904</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3777.9</v>
+        <v>1662.2</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>409.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>912.2</v>
+        <v>110.7</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1108.5</v>
+        <v>219.7</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.595</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Rachel Qureshi; Ravi Yamamoto; Ahmed Brown; Rachel Kim</t>
+          <t>Jennifer Rossi; Robert Anderson</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Iris Partners</t>
+          <t>Gravity Capital</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1881,52 +1885,52 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2014-11-08</t>
+          <t>2016-09-26</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>2018-01-13</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1122.3</v>
+        <v>1766.5</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3029.2</v>
+        <v>4071.4</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>264.8</v>
+        <v>449.9</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>250.8</v>
+        <v>537.8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1097.9</v>
+        <v>1529.2</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.87</v>
+        <v>0.269</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Rachel Chen; Matthew Ivanov; Thomas Ivanov; Andrew Schmidt; Wei Williams</t>
+          <t>Michael Kim; Amanda Chen; Laura Patel; Rachel Vega; James Fischer</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Glacier Networks</t>
+          <t>Cipher Health</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1936,58 +1940,62 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2014-05-27</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>2016-01-23</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>2020-11-04</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="n">
-        <v>152</v>
+        <v>713.3</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v/>
+        <v>630</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>41.2</v>
+        <v>162</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v/>
+        <v>168.1</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>74.2</v>
+        <v>686.5</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.796</v>
+        <v>0.524</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Amanda Qureshi; Hannah Nakamura</t>
+          <t>Priya Mueller; Hannah Hassan; David Ivanov; Mark Vega</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Krypton Logic</t>
+          <t>Stratus Pharma</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1997,57 +2005,57 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2012-04-18</t>
+          <t>2014-01-15</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2019-02-19</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1229.3</v>
+        <v>893.4</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2817.8</v>
+        <v>1444.4</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>323.5</v>
+        <v>227.1</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>578.3</v>
+        <v>463.4</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>226.6</v>
+        <v>198.1</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.18</v>
+        <v>0.545</v>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Michael Fischer; Ravi Kim; Olivia Evans; Elena Xu; Olivia Williams</t>
+          <t>Sarah Williams; Andrew Qureshi; Matthew Patel; Mark Hassan</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>Fund II</t>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Ember Industries</t>
+          <t>Echo Networks</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2057,35 +2065,35 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2017-02-22</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2020-04-14</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>805.5</v>
+        <v>647.9</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1873.7</v>
+        <v>1901.3</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>171.3</v>
+        <v>153.2</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>359.7</v>
+        <v>301</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>157.5</v>
+        <v>353.6</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.266</v>
+        <v>0.845</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>David Rossi; Jessica Anderson; Emma Tanaka; Jennifer Kim; Laura Tanaka</t>
+          <t>David Evans; Jessica Xu; Jessica Brown</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -2097,17 +2105,17 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Cipher Media</t>
+          <t>Vertex Networks</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2117,35 +2125,35 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2014-01-10</t>
+          <t>2014-05-25</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2020-02-23</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1459</v>
+        <v>1280.9</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4053.6</v>
+        <v>3500.2</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>341.1</v>
+        <v>114.2</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>624.9</v>
+        <v>142.9</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>642.4</v>
+        <v>281.1</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.957</v>
+        <v>0.948</v>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Christopher Mueller; Elena Lopez; Matthew Rossi; Andrew Vega</t>
+          <t>Robert Nakamura; Amanda Brown; Emma Patel</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2157,17 +2165,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Nimbus Partners</t>
+          <t>Helix Health</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2177,35 +2185,35 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2017-01-25</t>
+          <t>2016-10-09</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1233.3</v>
+        <v>1164.5</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1200.8</v>
+        <v>1216.7</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>292.7</v>
+        <v>310.7</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>712</v>
+        <v>376.8</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>273.8</v>
+        <v>381.5</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.198</v>
+        <v>0.983</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Ravi Yamamoto; Jessica Schmidt; Sarah Qureshi; Priya Evans</t>
+          <t>Matthew Yamamoto; Hannah Xu</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2217,7 +2225,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Quanta Group</t>
+          <t>Delta AG</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -2227,7 +2235,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2237,35 +2245,35 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
+          <t>2017-05-23</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2019-06-08</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1717.8</v>
+        <v>1554.9</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3584.1</v>
+        <v>1843.1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>236.6</v>
+        <v>335</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>577.3</v>
+        <v>779</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>636.5</v>
+        <v>645</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.658</v>
+        <v>0.198</v>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Ravi Anderson; Hannah Johnson; Jessica Rossi; Thomas Davis</t>
+          <t>Rachel Patel; Robert Rossi; Amanda Chen; James Anderson; Christopher Brown</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -2277,17 +2285,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Beacon Capital</t>
+          <t>Junction Logistics</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2297,35 +2305,35 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2017-03-05</t>
+          <t>2017-12-12</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>147.7</v>
+        <v>1852.1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>468</v>
+        <v>1811.2</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>22.4</v>
+        <v>233.8</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>41.3</v>
+        <v>252.8</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14</v>
+        <v>998.9</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.644</v>
+        <v>0.845</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Andrew Mueller; Yuki Ivanov; Jennifer Ueno</t>
+          <t>Matthew Ueno; Olivia Nakamura; Amanda Anderson; Rachel Kim; Robert Qureshi</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -2337,17 +2345,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Apex Foods</t>
+          <t>Meridian Materials</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2357,35 +2365,35 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2015-03-05</t>
+          <t>2014-06-01</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>2019-01-06</t>
+          <t>2019-08-05</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>303.4</v>
+        <v>1801.8</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>599.8</v>
+        <v>5183.2</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>72</v>
+        <v>194.9</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>147.4</v>
+        <v>304.2</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>121.5</v>
+        <v>683.8</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.616</v>
+        <v>0.472</v>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Yuki Lopez; Michael Evans; Matthew Patel; Daniel Tanaka; Jennifer Yamamoto</t>
+          <t>Emma Rossi; Daniel Williams; Christopher Kim</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -2397,7 +2405,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Cobalt Health</t>
+          <t>Junction Partners</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -2407,7 +2415,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2417,113 +2425,117 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2017-05-23</t>
+          <t>2019-12-15</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>923.3</v>
+        <v>1914</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1424.4</v>
+        <v>6182.5</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>208</v>
+        <v>261.2</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>445.2</v>
+        <v>214</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>784</v>
+        <v>392</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.444</v>
+        <v>0.588</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Ravi Ueno; Robert Rossi; Yuki Patel</t>
+          <t>David Tanaka; Wei Ueno; Yuki Patel</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Apex Labs</t>
+          <t>Forge Industries</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr"/>
+          <t>2017-08-03</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n">
-        <v>477.1</v>
+        <v>753.7</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v/>
+        <v>759.7</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>41.7</v>
+        <v>67.2</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v/>
+        <v>92.59999999999999</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>107.6</v>
+        <v>272.2</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.269</v>
+        <v>0.529</v>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Daniel Qureshi; Elena Kim; Olivia Qureshi; Thomas Tanaka</t>
+          <t>Christopher Rossi; Andrew Ivanov</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Lattice Health</t>
+          <t>Krypton Partners</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2533,57 +2545,57 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2014-02-23</t>
+          <t>2019-08-17</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>2019-01-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>576.1</v>
+        <v>1444.8</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>477</v>
+        <v>1116.6</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>56.7</v>
+        <v>335.1</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>54.3</v>
+        <v>345.3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>167.9</v>
+        <v>462.7</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.893</v>
+        <v>0.873</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>David Hassan; Michael Tanaka</t>
+          <t>Michael Zhang; Michael Mueller; Amanda Evans; Emma Kim</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Quanta Tech</t>
+          <t>Meridian Inc</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2593,57 +2605,57 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2014-05-25</t>
+          <t>2018-12-24</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
+          <t>2022-12-16</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1823.9</v>
+        <v>246.6</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>5214.4</v>
+        <v>829.9</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>461.5</v>
+        <v>55.7</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>880.2</v>
+        <v>68.7</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1049.7</v>
+        <v>47.5</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.377</v>
+        <v>0.598</v>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>James Vega; Mark Qureshi; David Qureshi; Olivia Patel</t>
+          <t>Amanda Yamamoto; Sarah Mueller; Christopher Hassan</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Fund III</t>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Orion Labs</t>
+          <t>Cobalt Foods</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2653,35 +2665,35 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2016-08-12</t>
+          <t>2017-03-24</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1921.2</v>
+        <v>1337</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>5565.7</v>
+        <v>4202.7</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>236.4</v>
+        <v>348.3</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>586.4</v>
+        <v>473.2</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>740.9</v>
+        <v>561.6</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.457</v>
+        <v>0.866</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Jessica Tanaka; Robert Lopez</t>
+          <t>Rachel Tanaka; Hannah Ivanov; Sarah Gupta</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -2693,7 +2705,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Ember Holdings</t>
+          <t>Junction SA</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -2713,35 +2725,35 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2018-03-19</t>
+          <t>2016-08-05</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1742.3</v>
+        <v>1051.3</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>3933.9</v>
+        <v>2770.2</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>307.6</v>
+        <v>91.7</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>310.1</v>
+        <v>88.2</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.54</v>
+        <v>0.331</v>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Sophie Kim; Mark Fischer; Olivia Ueno; Mark Vega; Elena Davis</t>
+          <t>Sophie Davis; Priya Brown; Jessica Rossi</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -2753,17 +2765,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Junction Logic</t>
+          <t>Radial Foods</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2773,35 +2785,35 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2016-07-27</t>
+          <t>2019-09-10</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2022-09-18</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1402</v>
+        <v>1607.7</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2862.1</v>
+        <v>1505.2</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>205.7</v>
+        <v>389.7</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>390.4</v>
+        <v>907.2</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>146.5</v>
+        <v>1450.3</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.829</v>
+        <v>0.509</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>David Qureshi; Sophie Davis; Mark Davis; Rachel Schmidt</t>
+          <t>Sarah Ivanov; Wei Qureshi</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -2813,7 +2825,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Tessera Foods</t>
+          <t>Indigo SA</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -2823,41 +2835,45 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2019-02-24</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr"/>
+          <t>2019-12-16</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="n">
-        <v>740.1</v>
+        <v>1895.2</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v/>
+        <v>2494.7</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>69.09999999999999</v>
+        <v>394.9</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v/>
+        <v>861.7</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>278.8</v>
+        <v>659.4</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.57</v>
+        <v>0.837</v>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Ravi Hassan; Christopher Kim; Laura Ueno; David Xu</t>
+          <t>Thomas Vega; Daniel Nakamura</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -2869,17 +2885,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Orion Logistics</t>
+          <t>Fathom Dynamics</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2889,35 +2905,35 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2018-11-03</t>
+          <t>2019-05-15</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1954.8</v>
+        <v>1365.1</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>6653.5</v>
+        <v>1067.9</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>465.5</v>
+        <v>255.5</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>609.4</v>
+        <v>210.5</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1016.7</v>
+        <v>657.2</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.63</v>
+        <v>0.709</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Hannah Tanaka; Mark Johnson</t>
+          <t>Thomas Gupta; Yuki Anderson; Laura Williams; Thomas Xu</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -2929,17 +2945,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Orion Capital</t>
+          <t>Fathom Energy</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2949,35 +2965,35 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2019-04-06</t>
+          <t>2018-09-17</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1587.1</v>
+        <v>821.3</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>4637.5</v>
+        <v>1077.9</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>318.2</v>
+        <v>190.8</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>698.8</v>
+        <v>252.2</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1182.3</v>
+        <v>352.8</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>0.699</v>
+        <v>0.867</v>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Sophie Davis; Robert Vega</t>
+          <t>Mark Xu; Amanda Williams; Thomas Nakamura; Ravi Rossi; Priya Lopez</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -2989,17 +3005,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Drift Tech</t>
+          <t>Meridian Networks</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -3009,35 +3025,35 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2016-08-08</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
+          <t>2022-08-03</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1538</v>
+        <v>79.2</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>3856</v>
+        <v>119.2</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>145.4</v>
+        <v>15.2</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>202.6</v>
+        <v>21</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>567.7</v>
+        <v>19.6</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.282</v>
+        <v>0.42</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Williams; Laura Qureshi</t>
+          <t>Laura Fischer; Robert Brown; Laura Brown</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -3049,17 +3065,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Stratus SA</t>
+          <t>Fathom Inc</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3069,35 +3085,35 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2019-11-24</t>
+          <t>2017-05-25</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>531.8</v>
+        <v>1919.5</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1316.4</v>
+        <v>6030.2</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>96.3</v>
+        <v>508.8</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>184</v>
+        <v>1031.1</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>288.8</v>
+        <v>1001</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.324</v>
+        <v>0.526</v>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Matthew Mueller; Priya Qureshi; Laura Brown; Ahmed O'Brien; Yuki Kim</t>
+          <t>Yuki Zhang; Christopher Gupta; Robert Brown</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -3109,17 +3125,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Tessera Networks</t>
+          <t>Apex Logic</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3129,35 +3145,35 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2018-08-11</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1603.1</v>
+        <v>1867.3</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>4821.3</v>
+        <v>4364.4</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>363.8</v>
+        <v>501.6</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>412.2</v>
+        <v>422.6</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>661.5</v>
+        <v>1415.9</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.648</v>
+        <v>0.174</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Amanda Ueno; Laura Zhang; Ahmed Davis; Sarah Nakamura</t>
+          <t>Rachel Qureshi; Elena Evans; Ahmed Evans; Priya Hassan</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -3169,17 +3185,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Polaris Dynamics</t>
+          <t>Halo Pharma</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3189,7 +3205,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2018-09-09</t>
+          <t>2019-05-14</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -3198,26 +3214,26 @@
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>368.9</v>
+        <v>237.9</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>542.9</v>
+        <v>216.6</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>68.5</v>
+        <v>29.1</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>128.7</v>
+        <v>31.2</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>302</v>
+        <v>32.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>0.604</v>
+        <v>0.63</v>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Sophie Gupta; Jessica Schmidt; Wei Xu; Emma Williams; Amanda Rossi</t>
+          <t>Sarah Chen; Ravi Ueno; Michael Ueno; Daniel Brown; Amanda Ivanov</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
